--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130053968</v>
       </c>
       <c r="B2" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130053968</v>
+        <v>61741181</v>
       </c>
       <c r="B2" t="n">
-        <v>58198</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378855</v>
+        <v>378865</v>
       </c>
       <c r="R2" t="n">
-        <v>6286902</v>
+        <v>6286877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2016-10-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2016-10-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +779,224 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>98292471</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Halmstad, Torvsjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>378708</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6286959</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-01-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-01-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130053968</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Halmstad, Torvsjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>378855</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6286902</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98292471</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61741181</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053968</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61741181</v>
+        <v>135660745</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103023</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378865</v>
+        <v>378669</v>
       </c>
       <c r="R3" t="n">
-        <v>6286877</v>
+        <v>6286942</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-10-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-10-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,13 +902,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61741181</t>
+          <t>https://artportalen.se/Sighting/135660745</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130053968</v>
+        <v>61741181</v>
       </c>
       <c r="B4" t="n">
         <v>58327</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378855</v>
+        <v>378865</v>
       </c>
       <c r="R4" t="n">
-        <v>6286902</v>
+        <v>6286877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,22 +973,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2016-10-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2016-10-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +1013,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61741181</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130053968</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Halmstad, Torvsjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>378855</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6286902</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130053968</t>
         </is>
@@ -1023,6 +1135,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135660745</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135660745</v>
       </c>
       <c r="B3" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135660745</v>
       </c>
       <c r="B3" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40589-2023 artfynd.xlsx
+++ b/artfynd/A 40589-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135660745</v>
       </c>
       <c r="B3" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
